--- a/Lab1_D7Report/analysis/TaLEs-D7/draft1.xlsx
+++ b/Lab1_D7Report/analysis/TaLEs-D7/draft1.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\APLabR_TaLEs\Lab1_D7Report\analysis\TaLEs-D7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B15F982-3124-4E20-99B6-3383A7F60AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD1D018-1FDC-400A-9D1D-EB5C68C3E16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-68" yWindow="-68" windowWidth="19335" windowHeight="11416" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
   <si>
     <t>测量次数</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,6 +96,61 @@
   </si>
   <si>
     <t>theta</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试端子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Φ1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Φ2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>频率（kHz）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周期（mus）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUBCK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>H1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -859,4 +916,125 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A39CDD7-D15D-4653-A8CC-40CF69B1BF02}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="13.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2">
+        <f>1000/B3</f>
+        <v>6896.5517241379312</v>
+      </c>
+      <c r="C2" s="2">
+        <f t="shared" ref="C2:E2" si="0">1000/C3</f>
+        <v>1.3908205841446453</v>
+      </c>
+      <c r="D2" s="2">
+        <f t="shared" si="0"/>
+        <v>2.7777777777777777</v>
+      </c>
+      <c r="E2" s="2">
+        <f t="shared" si="0"/>
+        <v>2.7777777777777777</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="C3">
+        <v>719</v>
+      </c>
+      <c r="D3">
+        <v>360</v>
+      </c>
+      <c r="E3">
+        <v>360</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787C9A58-4E89-4EF2-A40C-1F5559A8A3F3}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>